--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0003T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0003T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.35575255147019</v>
+        <v>8.020309789613906</v>
       </c>
       <c r="D2" t="n">
-        <v>49.81869626260728</v>
+        <v>8.095538142673682</v>
       </c>
       <c r="E2" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F2" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.2564594036927</v>
+        <v>7.516674653100064</v>
       </c>
       <c r="D3" t="n">
-        <v>48.64885341568054</v>
+        <v>7.905438680048088</v>
       </c>
       <c r="E3" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F3" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.98568803888928</v>
+        <v>4.060174306319507</v>
       </c>
       <c r="D4" t="n">
-        <v>25.20245084082849</v>
+        <v>4.09539826163463</v>
       </c>
       <c r="E4" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F4" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.85419881410061</v>
+        <v>2.90130730729135</v>
       </c>
       <c r="D5" t="n">
-        <v>18.90142927067046</v>
+        <v>3.07148225648395</v>
       </c>
       <c r="E5" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F5" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.33003499425551</v>
+        <v>7.04113068656652</v>
       </c>
       <c r="D6" t="n">
-        <v>45.28203507712536</v>
+        <v>7.358330700032872</v>
       </c>
       <c r="E6" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F6" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.36120656072305</v>
+        <v>4.446196066117496</v>
       </c>
       <c r="D7" t="n">
-        <v>28.45058684539874</v>
+        <v>4.623220362377296</v>
       </c>
       <c r="E7" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F7" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.71721087255533</v>
+        <v>4.016546766790241</v>
       </c>
       <c r="D8" t="n">
-        <v>22.64220641345363</v>
+        <v>3.679358542186215</v>
       </c>
       <c r="E8" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F8" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.36420672282942</v>
+        <v>2.334183592459781</v>
       </c>
       <c r="D9" t="n">
-        <v>11.98381482556794</v>
+        <v>1.947369909154791</v>
       </c>
       <c r="E9" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F9" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.81956414486132</v>
+        <v>6.633179173539964</v>
       </c>
       <c r="D10" t="n">
-        <v>41.904233793024</v>
+        <v>6.8094379913664</v>
       </c>
       <c r="E10" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F10" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>28.73038829719977</v>
+        <v>4.668688098294964</v>
       </c>
       <c r="D11" t="n">
-        <v>28.6733623518179</v>
+        <v>4.659421382170409</v>
       </c>
       <c r="E11" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F11" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.34821391212398</v>
+        <v>5.744084760720147</v>
       </c>
       <c r="D12" t="n">
-        <v>35.73168698838846</v>
+        <v>5.806399135613125</v>
       </c>
       <c r="E12" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F12" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>26.56353076590548</v>
+        <v>4.31657374945964</v>
       </c>
       <c r="D13" t="n">
-        <v>25.22479236835633</v>
+        <v>4.099028759857903</v>
       </c>
       <c r="E13" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F13" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>47.83933627896336</v>
+        <v>7.773892145331546</v>
       </c>
       <c r="D14" t="n">
-        <v>48.17504914554076</v>
+        <v>7.828445486150374</v>
       </c>
       <c r="E14" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F14" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>49.68884045558436</v>
+        <v>8.074436574032458</v>
       </c>
       <c r="D15" t="n">
-        <v>47.28857429681626</v>
+        <v>7.684393323232642</v>
       </c>
       <c r="E15" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F15" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>44.87731918271934</v>
+        <v>7.292564367191893</v>
       </c>
       <c r="D16" t="n">
-        <v>44.41127739368018</v>
+        <v>7.216832576473029</v>
       </c>
       <c r="E16" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F16" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>47.89433348294267</v>
+        <v>7.782829190978184</v>
       </c>
       <c r="D17" t="n">
-        <v>45.58112822923462</v>
+        <v>7.406933337250626</v>
       </c>
       <c r="E17" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F17" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>45.37959315440917</v>
+        <v>7.37418388759149</v>
       </c>
       <c r="D18" t="n">
-        <v>43.915265676274</v>
+        <v>7.136230672394526</v>
       </c>
       <c r="E18" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F18" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>51.58226536100898</v>
+        <v>8.382118121163959</v>
       </c>
       <c r="D19" t="n">
-        <v>50.35561261762673</v>
+        <v>8.182787050364345</v>
       </c>
       <c r="E19" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F19" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>51.76655119708457</v>
+        <v>8.412064569526244</v>
       </c>
       <c r="D20" t="n">
-        <v>49.72204297216954</v>
+        <v>8.07983198297755</v>
       </c>
       <c r="E20" t="n">
-        <v>11.89260669964109</v>
+        <v>1.932548588691678</v>
       </c>
       <c r="F20" t="n">
-        <v>11.95871355593701</v>
+        <v>1.943290952839765</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
